--- a/public/converted/rasprodazha-16-mln-sverka-s-ut-68.xlsx
+++ b/public/converted/rasprodazha-16-mln-sverka-s-ut-68.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -65,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -76,16 +74,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,22 +448,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,40 +489,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>кол-во паллет</t>
+          <t>Цена с НДС</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>кол-во единиц на палете было</t>
+          <t>Сумма было</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>кол-во единиц на палете из счёта</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена с НДС</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>цена за паллет было</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>цена за паллет из счёта</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Сумма было</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Сумма из счёта</t>
         </is>
@@ -561,34 +523,15 @@
       <c r="E2" s="3" t="n">
         <v>1456</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>35</v>
+      <c r="F2" s="4" t="n">
+        <v>903.0769230769231</v>
       </c>
       <c r="G2" s="4">
-        <f>D2/F2</f>
+        <f>F2*D2</f>
         <v/>
       </c>
       <c r="H2" s="4">
-        <f>E2/F2</f>
-        <v/>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>903.0769230769231</v>
-      </c>
-      <c r="J2" s="5">
-        <f>L2/F2</f>
-        <v/>
-      </c>
-      <c r="K2" s="5">
-        <f>M2/F2</f>
-        <v/>
-      </c>
-      <c r="L2" s="5">
-        <f>I2*D2</f>
-        <v/>
-      </c>
-      <c r="M2" s="5">
-        <f>I2*E2</f>
+        <f>F2*E2</f>
         <v/>
       </c>
     </row>
@@ -612,34 +555,15 @@
       <c r="E3" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>11</v>
+      <c r="F3" s="4" t="n">
+        <v>294.6153846153846</v>
       </c>
       <c r="G3" s="4">
-        <f>D3/F3</f>
+        <f>F3*D3</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>E3/F3</f>
-        <v/>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>294.6153846153846</v>
-      </c>
-      <c r="J3" s="5">
-        <f>L3/F3</f>
-        <v/>
-      </c>
-      <c r="K3" s="5">
-        <f>M3/F3</f>
-        <v/>
-      </c>
-      <c r="L3" s="5">
-        <f>I3*D3</f>
-        <v/>
-      </c>
-      <c r="M3" s="5">
-        <f>I3*E3</f>
+        <f>F3*E3</f>
         <v/>
       </c>
     </row>
@@ -663,34 +587,15 @@
       <c r="E4" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>19</v>
+      <c r="F4" s="4" t="n">
+        <v>453.8461538461538</v>
       </c>
       <c r="G4" s="4">
-        <f>D4/F4</f>
+        <f>F4*D4</f>
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>E4/F4</f>
-        <v/>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>453.8461538461538</v>
-      </c>
-      <c r="J4" s="5">
-        <f>L4/F4</f>
-        <v/>
-      </c>
-      <c r="K4" s="5">
-        <f>M4/F4</f>
-        <v/>
-      </c>
-      <c r="L4" s="5">
-        <f>I4*D4</f>
-        <v/>
-      </c>
-      <c r="M4" s="5">
-        <f>I4*E4</f>
+        <f>F4*E4</f>
         <v/>
       </c>
     </row>
@@ -714,34 +619,15 @@
       <c r="E5" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>10</v>
+      <c r="F5" s="4" t="n">
+        <v>349.2307692307692</v>
       </c>
       <c r="G5" s="4">
-        <f>D5/F5</f>
+        <f>F5*D5</f>
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>E5/F5</f>
-        <v/>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>349.2307692307692</v>
-      </c>
-      <c r="J5" s="5">
-        <f>L5/F5</f>
-        <v/>
-      </c>
-      <c r="K5" s="5">
-        <f>M5/F5</f>
-        <v/>
-      </c>
-      <c r="L5" s="5">
-        <f>I5*D5</f>
-        <v/>
-      </c>
-      <c r="M5" s="5">
-        <f>I5*E5</f>
+        <f>F5*E5</f>
         <v/>
       </c>
     </row>
@@ -765,34 +651,15 @@
       <c r="E6" s="3" t="n">
         <v>1449</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>9</v>
+      <c r="F6" s="4" t="n">
+        <v>203.8461538461538</v>
       </c>
       <c r="G6" s="4">
-        <f>D6/F6</f>
+        <f>F6*D6</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>E6/F6</f>
-        <v/>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>203.8461538461538</v>
-      </c>
-      <c r="J6" s="5">
-        <f>L6/F6</f>
-        <v/>
-      </c>
-      <c r="K6" s="5">
-        <f>M6/F6</f>
-        <v/>
-      </c>
-      <c r="L6" s="5">
-        <f>I6*D6</f>
-        <v/>
-      </c>
-      <c r="M6" s="5">
-        <f>I6*E6</f>
+        <f>F6*E6</f>
         <v/>
       </c>
     </row>
@@ -816,34 +683,15 @@
       <c r="E7" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>7</v>
+      <c r="F7" s="4" t="n">
+        <v>128.4615384615385</v>
       </c>
       <c r="G7" s="4">
-        <f>D7/F7</f>
+        <f>F7*D7</f>
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>E7/F7</f>
-        <v/>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>128.4615384615385</v>
-      </c>
-      <c r="J7" s="5">
-        <f>L7/F7</f>
-        <v/>
-      </c>
-      <c r="K7" s="5">
-        <f>M7/F7</f>
-        <v/>
-      </c>
-      <c r="L7" s="5">
-        <f>I7*D7</f>
-        <v/>
-      </c>
-      <c r="M7" s="5">
-        <f>I7*E7</f>
+        <f>F7*E7</f>
         <v/>
       </c>
     </row>
@@ -867,34 +715,15 @@
       <c r="E8" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>2</v>
+      <c r="F8" s="4" t="n">
+        <v>14.65384615384615</v>
       </c>
       <c r="G8" s="4">
-        <f>D8/F8</f>
+        <f>F8*D8</f>
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>E8/F8</f>
-        <v/>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>14.65384615384615</v>
-      </c>
-      <c r="J8" s="5">
-        <f>L8/F8</f>
-        <v/>
-      </c>
-      <c r="K8" s="5">
-        <f>M8/F8</f>
-        <v/>
-      </c>
-      <c r="L8" s="5">
-        <f>I8*D8</f>
-        <v/>
-      </c>
-      <c r="M8" s="5">
-        <f>I8*E8</f>
+        <f>F8*E8</f>
         <v/>
       </c>
     </row>
@@ -918,34 +747,15 @@
       <c r="E9" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>2</v>
+      <c r="F9" s="4" t="n">
+        <v>52.48461538461539</v>
       </c>
       <c r="G9" s="4">
-        <f>D9/F9</f>
+        <f>F9*D9</f>
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>E9/F9</f>
-        <v/>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>52.48461538461539</v>
-      </c>
-      <c r="J9" s="5">
-        <f>L9/F9</f>
-        <v/>
-      </c>
-      <c r="K9" s="5">
-        <f>M9/F9</f>
-        <v/>
-      </c>
-      <c r="L9" s="5">
-        <f>I9*D9</f>
-        <v/>
-      </c>
-      <c r="M9" s="5">
-        <f>I9*E9</f>
+        <f>F9*E9</f>
         <v/>
       </c>
     </row>
@@ -969,34 +779,15 @@
       <c r="E10" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>3</v>
+      <c r="F10" s="4" t="n">
+        <v>144.1076923076923</v>
       </c>
       <c r="G10" s="4">
-        <f>D10/F10</f>
+        <f>F10*D10</f>
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>E10/F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>144.1076923076923</v>
-      </c>
-      <c r="J10" s="5">
-        <f>L10/F10</f>
-        <v/>
-      </c>
-      <c r="K10" s="5">
-        <f>M10/F10</f>
-        <v/>
-      </c>
-      <c r="L10" s="5">
-        <f>I10*D10</f>
-        <v/>
-      </c>
-      <c r="M10" s="5">
-        <f>I10*E10</f>
+        <f>F10*E10</f>
         <v/>
       </c>
     </row>
@@ -1024,34 +815,15 @@
       <c r="E11" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>3</v>
+      <c r="F11" s="4" t="n">
+        <v>301.5384615384615</v>
       </c>
       <c r="G11" s="4">
-        <f>D11/F11</f>
+        <f>F11*D11</f>
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>E11/F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>301.5384615384615</v>
-      </c>
-      <c r="J11" s="5">
-        <f>L11/F11</f>
-        <v/>
-      </c>
-      <c r="K11" s="5">
-        <f>M11/F11</f>
-        <v/>
-      </c>
-      <c r="L11" s="5">
-        <f>I11*D11</f>
-        <v/>
-      </c>
-      <c r="M11" s="5">
-        <f>I11*E11</f>
+        <f>F11*E11</f>
         <v/>
       </c>
     </row>
@@ -1075,34 +847,15 @@
       <c r="E12" s="3" t="n">
         <v>1462</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>9</v>
+      <c r="F12" s="4" t="n">
+        <v>376.9230769230769</v>
       </c>
       <c r="G12" s="4">
-        <f>D12/F12</f>
+        <f>F12*D12</f>
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>E12/F12</f>
-        <v/>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>376.9230769230769</v>
-      </c>
-      <c r="J12" s="5">
-        <f>L12/F12</f>
-        <v/>
-      </c>
-      <c r="K12" s="5">
-        <f>M12/F12</f>
-        <v/>
-      </c>
-      <c r="L12" s="5">
-        <f>I12*D12</f>
-        <v/>
-      </c>
-      <c r="M12" s="5">
-        <f>I12*E12</f>
+        <f>F12*E12</f>
         <v/>
       </c>
     </row>
@@ -1126,34 +879,15 @@
       <c r="E13" s="3" t="n">
         <v>1453</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>23</v>
+      <c r="F13" s="4" t="n">
+        <v>186.1538461538462</v>
       </c>
       <c r="G13" s="4">
-        <f>D13/F13</f>
+        <f>F13*D13</f>
         <v/>
       </c>
       <c r="H13" s="4">
-        <f>E13/F13</f>
-        <v/>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>186.1538461538462</v>
-      </c>
-      <c r="J13" s="5">
-        <f>L13/F13</f>
-        <v/>
-      </c>
-      <c r="K13" s="5">
-        <f>M13/F13</f>
-        <v/>
-      </c>
-      <c r="L13" s="5">
-        <f>I13*D13</f>
-        <v/>
-      </c>
-      <c r="M13" s="5">
-        <f>I13*E13</f>
+        <f>F13*E13</f>
         <v/>
       </c>
     </row>
@@ -1177,34 +911,15 @@
       <c r="E14" s="3" t="n">
         <v>1456</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>35</v>
+      <c r="F14" s="4" t="n">
+        <v>1023.846153846154</v>
       </c>
       <c r="G14" s="4">
-        <f>D14/F14</f>
+        <f>F14*D14</f>
         <v/>
       </c>
       <c r="H14" s="4">
-        <f>E14/F14</f>
-        <v/>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>1023.846153846154</v>
-      </c>
-      <c r="J14" s="5">
-        <f>L14/F14</f>
-        <v/>
-      </c>
-      <c r="K14" s="5">
-        <f>M14/F14</f>
-        <v/>
-      </c>
-      <c r="L14" s="5">
-        <f>I14*D14</f>
-        <v/>
-      </c>
-      <c r="M14" s="5">
-        <f>I14*E14</f>
+        <f>F14*E14</f>
         <v/>
       </c>
     </row>
@@ -1228,34 +943,15 @@
       <c r="E15" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>52</v>
+      <c r="F15" s="4" t="n">
+        <v>1384.946153846154</v>
       </c>
       <c r="G15" s="4">
-        <f>D15/F15</f>
+        <f>F15*D15</f>
         <v/>
       </c>
       <c r="H15" s="4">
-        <f>E15/F15</f>
-        <v/>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>1384.946153846154</v>
-      </c>
-      <c r="J15" s="5">
-        <f>L15/F15</f>
-        <v/>
-      </c>
-      <c r="K15" s="5">
-        <f>M15/F15</f>
-        <v/>
-      </c>
-      <c r="L15" s="5">
-        <f>I15*D15</f>
-        <v/>
-      </c>
-      <c r="M15" s="5">
-        <f>I15*E15</f>
+        <f>F15*E15</f>
         <v/>
       </c>
     </row>
@@ -1279,34 +975,15 @@
       <c r="E16" s="3" t="n">
         <v>2925</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>5</v>
+      <c r="F16" s="4" t="n">
+        <v>51.79230769230769</v>
       </c>
       <c r="G16" s="4">
-        <f>D16/F16</f>
+        <f>F16*D16</f>
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>E16/F16</f>
-        <v/>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>51.79230769230769</v>
-      </c>
-      <c r="J16" s="5">
-        <f>L16/F16</f>
-        <v/>
-      </c>
-      <c r="K16" s="5">
-        <f>M16/F16</f>
-        <v/>
-      </c>
-      <c r="L16" s="5">
-        <f>I16*D16</f>
-        <v/>
-      </c>
-      <c r="M16" s="5">
-        <f>I16*E16</f>
+        <f>F16*E16</f>
         <v/>
       </c>
     </row>
@@ -1330,34 +1007,15 @@
       <c r="E17" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>6</v>
+      <c r="F17" s="4" t="n">
+        <v>124</v>
       </c>
       <c r="G17" s="4">
-        <f>D17/F17</f>
+        <f>F17*D17</f>
         <v/>
       </c>
       <c r="H17" s="4">
-        <f>E17/F17</f>
-        <v/>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="J17" s="5">
-        <f>L17/F17</f>
-        <v/>
-      </c>
-      <c r="K17" s="5">
-        <f>M17/F17</f>
-        <v/>
-      </c>
-      <c r="L17" s="5">
-        <f>I17*D17</f>
-        <v/>
-      </c>
-      <c r="M17" s="5">
-        <f>I17*E17</f>
+        <f>F17*E17</f>
         <v/>
       </c>
     </row>
@@ -1381,34 +1039,15 @@
       <c r="E18" s="3" t="n">
         <v>1602</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>10</v>
+      <c r="F18" s="4" t="n">
+        <v>174</v>
       </c>
       <c r="G18" s="4">
-        <f>D18/F18</f>
+        <f>F18*D18</f>
         <v/>
       </c>
       <c r="H18" s="4">
-        <f>E18/F18</f>
-        <v/>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="J18" s="5">
-        <f>L18/F18</f>
-        <v/>
-      </c>
-      <c r="K18" s="5">
-        <f>M18/F18</f>
-        <v/>
-      </c>
-      <c r="L18" s="5">
-        <f>I18*D18</f>
-        <v/>
-      </c>
-      <c r="M18" s="5">
-        <f>I18*E18</f>
+        <f>F18*E18</f>
         <v/>
       </c>
     </row>
@@ -1432,34 +1071,15 @@
       <c r="E19" s="3" t="n">
         <v>1602</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>12</v>
+      <c r="F19" s="4" t="n">
+        <v>394</v>
       </c>
       <c r="G19" s="4">
-        <f>D19/F19</f>
+        <f>F19*D19</f>
         <v/>
       </c>
       <c r="H19" s="4">
-        <f>E19/F19</f>
-        <v/>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>394</v>
-      </c>
-      <c r="J19" s="5">
-        <f>L19/F19</f>
-        <v/>
-      </c>
-      <c r="K19" s="5">
-        <f>M19/F19</f>
-        <v/>
-      </c>
-      <c r="L19" s="5">
-        <f>I19*D19</f>
-        <v/>
-      </c>
-      <c r="M19" s="5">
-        <f>I19*E19</f>
+        <f>F19*E19</f>
         <v/>
       </c>
     </row>
@@ -1483,34 +1103,15 @@
       <c r="E20" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>4</v>
+      <c r="F20" s="4" t="n">
+        <v>92</v>
       </c>
       <c r="G20" s="4">
-        <f>D20/F20</f>
+        <f>F20*D20</f>
         <v/>
       </c>
       <c r="H20" s="4">
-        <f>E20/F20</f>
-        <v/>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="J20" s="5">
-        <f>L20/F20</f>
-        <v/>
-      </c>
-      <c r="K20" s="5">
-        <f>M20/F20</f>
-        <v/>
-      </c>
-      <c r="L20" s="5">
-        <f>I20*D20</f>
-        <v/>
-      </c>
-      <c r="M20" s="5">
-        <f>I20*E20</f>
+        <f>F20*E20</f>
         <v/>
       </c>
     </row>
@@ -1534,34 +1135,15 @@
       <c r="E21" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>7</v>
+      <c r="F21" s="4" t="n">
+        <v>72</v>
       </c>
       <c r="G21" s="4">
-        <f>D21/F21</f>
+        <f>F21*D21</f>
         <v/>
       </c>
       <c r="H21" s="4">
-        <f>E21/F21</f>
-        <v/>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="J21" s="5">
-        <f>L21/F21</f>
-        <v/>
-      </c>
-      <c r="K21" s="5">
-        <f>M21/F21</f>
-        <v/>
-      </c>
-      <c r="L21" s="5">
-        <f>I21*D21</f>
-        <v/>
-      </c>
-      <c r="M21" s="5">
-        <f>I21*E21</f>
+        <f>F21*E21</f>
         <v/>
       </c>
     </row>
@@ -1585,34 +1167,15 @@
       <c r="E22" s="3" t="n">
         <v>1597</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>15</v>
+      <c r="F22" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="G22" s="4">
-        <f>D22/F22</f>
+        <f>F22*D22</f>
         <v/>
       </c>
       <c r="H22" s="4">
-        <f>E22/F22</f>
-        <v/>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="J22" s="5">
-        <f>L22/F22</f>
-        <v/>
-      </c>
-      <c r="K22" s="5">
-        <f>M22/F22</f>
-        <v/>
-      </c>
-      <c r="L22" s="5">
-        <f>I22*D22</f>
-        <v/>
-      </c>
-      <c r="M22" s="5">
-        <f>I22*E22</f>
+        <f>F22*E22</f>
         <v/>
       </c>
     </row>
@@ -1636,34 +1199,15 @@
       <c r="E23" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>8</v>
+      <c r="F23" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="G23" s="4">
-        <f>D23/F23</f>
+        <f>F23*D23</f>
         <v/>
       </c>
       <c r="H23" s="4">
-        <f>E23/F23</f>
-        <v/>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="J23" s="5">
-        <f>L23/F23</f>
-        <v/>
-      </c>
-      <c r="K23" s="5">
-        <f>M23/F23</f>
-        <v/>
-      </c>
-      <c r="L23" s="5">
-        <f>I23*D23</f>
-        <v/>
-      </c>
-      <c r="M23" s="5">
-        <f>I23*E23</f>
+        <f>F23*E23</f>
         <v/>
       </c>
     </row>
@@ -1687,34 +1231,15 @@
       <c r="E24" s="3" t="n">
         <v>1597</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>9</v>
+      <c r="F24" s="4" t="n">
+        <v>196</v>
       </c>
       <c r="G24" s="4">
-        <f>D24/F24</f>
+        <f>F24*D24</f>
         <v/>
       </c>
       <c r="H24" s="4">
-        <f>E24/F24</f>
-        <v/>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>196</v>
-      </c>
-      <c r="J24" s="5">
-        <f>L24/F24</f>
-        <v/>
-      </c>
-      <c r="K24" s="5">
-        <f>M24/F24</f>
-        <v/>
-      </c>
-      <c r="L24" s="5">
-        <f>I24*D24</f>
-        <v/>
-      </c>
-      <c r="M24" s="5">
-        <f>I24*E24</f>
+        <f>F24*E24</f>
         <v/>
       </c>
     </row>
@@ -1738,34 +1263,15 @@
       <c r="E25" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>20</v>
+      <c r="F25" s="4" t="n">
+        <v>286</v>
       </c>
       <c r="G25" s="4">
-        <f>D25/F25</f>
+        <f>F25*D25</f>
         <v/>
       </c>
       <c r="H25" s="4">
-        <f>E25/F25</f>
-        <v/>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="J25" s="5">
-        <f>L25/F25</f>
-        <v/>
-      </c>
-      <c r="K25" s="5">
-        <f>M25/F25</f>
-        <v/>
-      </c>
-      <c r="L25" s="5">
-        <f>I25*D25</f>
-        <v/>
-      </c>
-      <c r="M25" s="5">
-        <f>I25*E25</f>
+        <f>F25*E25</f>
         <v/>
       </c>
     </row>
@@ -1789,34 +1295,15 @@
       <c r="E26" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>11</v>
+      <c r="F26" s="4" t="n">
+        <v>250</v>
       </c>
       <c r="G26" s="4">
-        <f>D26/F26</f>
+        <f>F26*D26</f>
         <v/>
       </c>
       <c r="H26" s="4">
-        <f>E26/F26</f>
-        <v/>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J26" s="5">
-        <f>L26/F26</f>
-        <v/>
-      </c>
-      <c r="K26" s="5">
-        <f>M26/F26</f>
-        <v/>
-      </c>
-      <c r="L26" s="5">
-        <f>I26*D26</f>
-        <v/>
-      </c>
-      <c r="M26" s="5">
-        <f>I26*E26</f>
+        <f>F26*E26</f>
         <v/>
       </c>
     </row>
@@ -1840,34 +1327,15 @@
       <c r="E27" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>28</v>
+      <c r="F27" s="4" t="n">
+        <v>134</v>
       </c>
       <c r="G27" s="4">
-        <f>D27/F27</f>
+        <f>F27*D27</f>
         <v/>
       </c>
       <c r="H27" s="4">
-        <f>E27/F27</f>
-        <v/>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="J27" s="5">
-        <f>L27/F27</f>
-        <v/>
-      </c>
-      <c r="K27" s="5">
-        <f>M27/F27</f>
-        <v/>
-      </c>
-      <c r="L27" s="5">
-        <f>I27*D27</f>
-        <v/>
-      </c>
-      <c r="M27" s="5">
-        <f>I27*E27</f>
+        <f>F27*E27</f>
         <v/>
       </c>
     </row>
@@ -1895,34 +1363,15 @@
       <c r="E28" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>17</v>
+      <c r="F28" s="4" t="n">
+        <v>220</v>
       </c>
       <c r="G28" s="4">
-        <f>D28/F28</f>
+        <f>F28*D28</f>
         <v/>
       </c>
       <c r="H28" s="4">
-        <f>E28/F28</f>
-        <v/>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="J28" s="5">
-        <f>L28/F28</f>
-        <v/>
-      </c>
-      <c r="K28" s="5">
-        <f>M28/F28</f>
-        <v/>
-      </c>
-      <c r="L28" s="5">
-        <f>I28*D28</f>
-        <v/>
-      </c>
-      <c r="M28" s="5">
-        <f>I28*E28</f>
+        <f>F28*E28</f>
         <v/>
       </c>
     </row>
@@ -1946,34 +1395,15 @@
       <c r="E29" s="3" t="n">
         <v>1495</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>3</v>
+      <c r="F29" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="G29" s="4">
-        <f>D29/F29</f>
+        <f>F29*D29</f>
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>E29/F29</f>
-        <v/>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="J29" s="5">
-        <f>L29/F29</f>
-        <v/>
-      </c>
-      <c r="K29" s="5">
-        <f>M29/F29</f>
-        <v/>
-      </c>
-      <c r="L29" s="5">
-        <f>I29*D29</f>
-        <v/>
-      </c>
-      <c r="M29" s="5">
-        <f>I29*E29</f>
+        <f>F29*E29</f>
         <v/>
       </c>
     </row>
@@ -1997,34 +1427,15 @@
       <c r="E30" s="3" t="n">
         <v>1481</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>13</v>
+      <c r="F30" s="4" t="n">
+        <v>114</v>
       </c>
       <c r="G30" s="4">
-        <f>D30/F30</f>
+        <f>F30*D30</f>
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>E30/F30</f>
-        <v/>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="J30" s="5">
-        <f>L30/F30</f>
-        <v/>
-      </c>
-      <c r="K30" s="5">
-        <f>M30/F30</f>
-        <v/>
-      </c>
-      <c r="L30" s="5">
-        <f>I30*D30</f>
-        <v/>
-      </c>
-      <c r="M30" s="5">
-        <f>I30*E30</f>
+        <f>F30*E30</f>
         <v/>
       </c>
     </row>
@@ -2048,34 +1459,15 @@
       <c r="E31" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>9</v>
+      <c r="F31" s="4" t="n">
+        <v>100</v>
       </c>
       <c r="G31" s="4">
-        <f>D31/F31</f>
+        <f>F31*D31</f>
         <v/>
       </c>
       <c r="H31" s="4">
-        <f>E31/F31</f>
-        <v/>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J31" s="5">
-        <f>L31/F31</f>
-        <v/>
-      </c>
-      <c r="K31" s="5">
-        <f>M31/F31</f>
-        <v/>
-      </c>
-      <c r="L31" s="5">
-        <f>I31*D31</f>
-        <v/>
-      </c>
-      <c r="M31" s="5">
-        <f>I31*E31</f>
+        <f>F31*E31</f>
         <v/>
       </c>
     </row>
@@ -2099,34 +1491,15 @@
       <c r="E32" s="3" t="n">
         <v>1492</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>3</v>
+      <c r="F32" s="4" t="n">
+        <v>224</v>
       </c>
       <c r="G32" s="4">
-        <f>D32/F32</f>
+        <f>F32*D32</f>
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>E32/F32</f>
-        <v/>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>224</v>
-      </c>
-      <c r="J32" s="5">
-        <f>L32/F32</f>
-        <v/>
-      </c>
-      <c r="K32" s="5">
-        <f>M32/F32</f>
-        <v/>
-      </c>
-      <c r="L32" s="5">
-        <f>I32*D32</f>
-        <v/>
-      </c>
-      <c r="M32" s="5">
-        <f>I32*E32</f>
+        <f>F32*E32</f>
         <v/>
       </c>
     </row>
@@ -2146,34 +1519,15 @@
       <c r="E33" s="3" t="n">
         <v>359</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
+      <c r="F33" s="4" t="n">
+        <v>64</v>
       </c>
       <c r="G33" s="4">
-        <f>D33/F33</f>
+        <f>F33*D33</f>
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>E33/F33</f>
-        <v/>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="J33" s="5">
-        <f>L33/F33</f>
-        <v/>
-      </c>
-      <c r="K33" s="5">
-        <f>M33/F33</f>
-        <v/>
-      </c>
-      <c r="L33" s="5">
-        <f>I33*D33</f>
-        <v/>
-      </c>
-      <c r="M33" s="5">
-        <f>I33*E33</f>
+        <f>F33*E33</f>
         <v/>
       </c>
     </row>
@@ -2193,34 +1547,15 @@
       <c r="E34" s="3" t="n">
         <v>371</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>1</v>
+      <c r="F34" s="4" t="n">
+        <v>70</v>
       </c>
       <c r="G34" s="4">
-        <f>D34/F34</f>
+        <f>F34*D34</f>
         <v/>
       </c>
       <c r="H34" s="4">
-        <f>E34/F34</f>
-        <v/>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="J34" s="5">
-        <f>L34/F34</f>
-        <v/>
-      </c>
-      <c r="K34" s="5">
-        <f>M34/F34</f>
-        <v/>
-      </c>
-      <c r="L34" s="5">
-        <f>I34*D34</f>
-        <v/>
-      </c>
-      <c r="M34" s="5">
-        <f>I34*E34</f>
+        <f>F34*E34</f>
         <v/>
       </c>
     </row>
@@ -2240,34 +1575,15 @@
       <c r="E35" s="3" t="n">
         <v>803</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>5</v>
+      <c r="F35" s="4" t="n">
+        <v>144</v>
       </c>
       <c r="G35" s="4">
-        <f>D35/F35</f>
+        <f>F35*D35</f>
         <v/>
       </c>
       <c r="H35" s="4">
-        <f>E35/F35</f>
-        <v/>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="J35" s="5">
-        <f>L35/F35</f>
-        <v/>
-      </c>
-      <c r="K35" s="5">
-        <f>M35/F35</f>
-        <v/>
-      </c>
-      <c r="L35" s="5">
-        <f>I35*D35</f>
-        <v/>
-      </c>
-      <c r="M35" s="5">
-        <f>I35*E35</f>
+        <f>F35*E35</f>
         <v/>
       </c>
     </row>
@@ -2287,34 +1603,15 @@
       <c r="E36" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1</v>
+      <c r="F36" s="4" t="n">
+        <v>160</v>
       </c>
       <c r="G36" s="4">
-        <f>D36/F36</f>
+        <f>F36*D36</f>
         <v/>
       </c>
       <c r="H36" s="4">
-        <f>E36/F36</f>
-        <v/>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="J36" s="5">
-        <f>L36/F36</f>
-        <v/>
-      </c>
-      <c r="K36" s="5">
-        <f>M36/F36</f>
-        <v/>
-      </c>
-      <c r="L36" s="5">
-        <f>I36*D36</f>
-        <v/>
-      </c>
-      <c r="M36" s="5">
-        <f>I36*E36</f>
+        <f>F36*E36</f>
         <v/>
       </c>
     </row>
@@ -2334,34 +1631,15 @@
       <c r="E37" s="3" t="n">
         <v>519</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>3</v>
+      <c r="F37" s="4" t="n">
+        <v>226</v>
       </c>
       <c r="G37" s="4">
-        <f>D37/F37</f>
+        <f>F37*D37</f>
         <v/>
       </c>
       <c r="H37" s="4">
-        <f>E37/F37</f>
-        <v/>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>226</v>
-      </c>
-      <c r="J37" s="5">
-        <f>L37/F37</f>
-        <v/>
-      </c>
-      <c r="K37" s="5">
-        <f>M37/F37</f>
-        <v/>
-      </c>
-      <c r="L37" s="5">
-        <f>I37*D37</f>
-        <v/>
-      </c>
-      <c r="M37" s="5">
-        <f>I37*E37</f>
+        <f>F37*E37</f>
         <v/>
       </c>
     </row>
@@ -2381,34 +1659,15 @@
       <c r="E38" s="3" t="n">
         <v>649</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>4</v>
+      <c r="F38" s="4" t="n">
+        <v>116</v>
       </c>
       <c r="G38" s="4">
-        <f>D38/F38</f>
+        <f>F38*D38</f>
         <v/>
       </c>
       <c r="H38" s="4">
-        <f>E38/F38</f>
-        <v/>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="J38" s="5">
-        <f>L38/F38</f>
-        <v/>
-      </c>
-      <c r="K38" s="5">
-        <f>M38/F38</f>
-        <v/>
-      </c>
-      <c r="L38" s="5">
-        <f>I38*D38</f>
-        <v/>
-      </c>
-      <c r="M38" s="5">
-        <f>I38*E38</f>
+        <f>F38*E38</f>
         <v/>
       </c>
     </row>
@@ -2428,34 +1687,15 @@
       <c r="E39" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>1</v>
+      <c r="F39" s="4" t="n">
+        <v>56</v>
       </c>
       <c r="G39" s="4">
-        <f>D39/F39</f>
+        <f>F39*D39</f>
         <v/>
       </c>
       <c r="H39" s="4">
-        <f>E39/F39</f>
-        <v/>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="J39" s="5">
-        <f>L39/F39</f>
-        <v/>
-      </c>
-      <c r="K39" s="5">
-        <f>M39/F39</f>
-        <v/>
-      </c>
-      <c r="L39" s="5">
-        <f>I39*D39</f>
-        <v/>
-      </c>
-      <c r="M39" s="5">
-        <f>I39*E39</f>
+        <f>F39*E39</f>
         <v/>
       </c>
     </row>
@@ -2475,34 +1715,15 @@
       <c r="E40" s="3" t="n">
         <v>911</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>2</v>
+      <c r="F40" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="G40" s="4">
-        <f>D40/F40</f>
+        <f>F40*D40</f>
         <v/>
       </c>
       <c r="H40" s="4">
-        <f>E40/F40</f>
-        <v/>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="J40" s="5">
-        <f>L40/F40</f>
-        <v/>
-      </c>
-      <c r="K40" s="5">
-        <f>M40/F40</f>
-        <v/>
-      </c>
-      <c r="L40" s="5">
-        <f>I40*D40</f>
-        <v/>
-      </c>
-      <c r="M40" s="5">
-        <f>I40*E40</f>
+        <f>F40*E40</f>
         <v/>
       </c>
     </row>
@@ -2522,34 +1743,15 @@
       <c r="E41" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>1</v>
+      <c r="F41" s="4" t="n">
+        <v>56</v>
       </c>
       <c r="G41" s="4">
-        <f>D41/F41</f>
+        <f>F41*D41</f>
         <v/>
       </c>
       <c r="H41" s="4">
-        <f>E41/F41</f>
-        <v/>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="J41" s="5">
-        <f>L41/F41</f>
-        <v/>
-      </c>
-      <c r="K41" s="5">
-        <f>M41/F41</f>
-        <v/>
-      </c>
-      <c r="L41" s="5">
-        <f>I41*D41</f>
-        <v/>
-      </c>
-      <c r="M41" s="5">
-        <f>I41*E41</f>
+        <f>F41*E41</f>
         <v/>
       </c>
     </row>
@@ -2569,34 +1771,15 @@
       <c r="E42" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
+      <c r="F42" s="4" t="n">
+        <v>56</v>
       </c>
       <c r="G42" s="4">
-        <f>D42/F42</f>
+        <f>F42*D42</f>
         <v/>
       </c>
       <c r="H42" s="4">
-        <f>E42/F42</f>
-        <v/>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="J42" s="5">
-        <f>L42/F42</f>
-        <v/>
-      </c>
-      <c r="K42" s="5">
-        <f>M42/F42</f>
-        <v/>
-      </c>
-      <c r="L42" s="5">
-        <f>I42*D42</f>
-        <v/>
-      </c>
-      <c r="M42" s="5">
-        <f>I42*E42</f>
+        <f>F42*E42</f>
         <v/>
       </c>
     </row>
@@ -2616,34 +1799,15 @@
       <c r="E43" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>9</v>
+      <c r="F43" s="4" t="n">
+        <v>274</v>
       </c>
       <c r="G43" s="4">
-        <f>D43/F43</f>
+        <f>F43*D43</f>
         <v/>
       </c>
       <c r="H43" s="4">
-        <f>E43/F43</f>
-        <v/>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>274</v>
-      </c>
-      <c r="J43" s="5">
-        <f>L43/F43</f>
-        <v/>
-      </c>
-      <c r="K43" s="5">
-        <f>M43/F43</f>
-        <v/>
-      </c>
-      <c r="L43" s="5">
-        <f>I43*D43</f>
-        <v/>
-      </c>
-      <c r="M43" s="5">
-        <f>I43*E43</f>
+        <f>F43*E43</f>
         <v/>
       </c>
     </row>
@@ -2663,34 +1827,15 @@
       <c r="E44" s="3" t="n">
         <v>323</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>1</v>
+      <c r="F44" s="4" t="n">
+        <v>116</v>
       </c>
       <c r="G44" s="4">
-        <f>D44/F44</f>
+        <f>F44*D44</f>
         <v/>
       </c>
       <c r="H44" s="4">
-        <f>E44/F44</f>
-        <v/>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="J44" s="5">
-        <f>L44/F44</f>
-        <v/>
-      </c>
-      <c r="K44" s="5">
-        <f>M44/F44</f>
-        <v/>
-      </c>
-      <c r="L44" s="5">
-        <f>I44*D44</f>
-        <v/>
-      </c>
-      <c r="M44" s="5">
-        <f>I44*E44</f>
+        <f>F44*E44</f>
         <v/>
       </c>
     </row>
@@ -2710,34 +1855,15 @@
       <c r="E45" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>1</v>
+      <c r="F45" s="4" t="n">
+        <v>90</v>
       </c>
       <c r="G45" s="4">
-        <f>D45/F45</f>
+        <f>F45*D45</f>
         <v/>
       </c>
       <c r="H45" s="4">
-        <f>E45/F45</f>
-        <v/>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="J45" s="5">
-        <f>L45/F45</f>
-        <v/>
-      </c>
-      <c r="K45" s="5">
-        <f>M45/F45</f>
-        <v/>
-      </c>
-      <c r="L45" s="5">
-        <f>I45*D45</f>
-        <v/>
-      </c>
-      <c r="M45" s="5">
-        <f>I45*E45</f>
+        <f>F45*E45</f>
         <v/>
       </c>
     </row>
@@ -2757,34 +1883,15 @@
       <c r="E46" s="3" t="n">
         <v>359</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>1</v>
+      <c r="F46" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="G46" s="4">
-        <f>D46/F46</f>
+        <f>F46*D46</f>
         <v/>
       </c>
       <c r="H46" s="4">
-        <f>E46/F46</f>
-        <v/>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="J46" s="5">
-        <f>L46/F46</f>
-        <v/>
-      </c>
-      <c r="K46" s="5">
-        <f>M46/F46</f>
-        <v/>
-      </c>
-      <c r="L46" s="5">
-        <f>I46*D46</f>
-        <v/>
-      </c>
-      <c r="M46" s="5">
-        <f>I46*E46</f>
+        <f>F46*E46</f>
         <v/>
       </c>
     </row>
@@ -2804,34 +1911,15 @@
       <c r="E47" s="3" t="n">
         <v>679</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>2</v>
+      <c r="F47" s="4" t="n">
+        <v>90</v>
       </c>
       <c r="G47" s="4">
-        <f>D47/F47</f>
+        <f>F47*D47</f>
         <v/>
       </c>
       <c r="H47" s="4">
-        <f>E47/F47</f>
-        <v/>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="J47" s="5">
-        <f>L47/F47</f>
-        <v/>
-      </c>
-      <c r="K47" s="5">
-        <f>M47/F47</f>
-        <v/>
-      </c>
-      <c r="L47" s="5">
-        <f>I47*D47</f>
-        <v/>
-      </c>
-      <c r="M47" s="5">
-        <f>I47*E47</f>
+        <f>F47*E47</f>
         <v/>
       </c>
     </row>
@@ -2843,29 +1931,21 @@
           <t>ИТОГО:</t>
         </is>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <f>SUM(D2:D47)</f>
         <v/>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="5">
         <f>SUM(E2:E47)</f>
         <v/>
       </c>
-      <c r="F48" s="6">
-        <f>SUM(F2:F47)</f>
-        <v/>
-      </c>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="8">
-        <f>SUM(L2:L47)</f>
-        <v/>
-      </c>
-      <c r="M48" s="8">
-        <f>SUM(M2:M47)</f>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6">
+        <f>SUM(G2:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="6">
+        <f>SUM(H2:H47)</f>
         <v/>
       </c>
     </row>

--- a/public/converted/rasprodazha-16-mln-sverka-s-ut-68.xlsx
+++ b/public/converted/rasprodazha-16-mln-sverka-s-ut-68.xlsx
@@ -448,17 +448,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,30 +475,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Наименование из счёта</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Характеристики</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Остатки из 1С на 07.10.2026 было</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Количество из счёта</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Цена с НДС</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Сумма было</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Сумма из счёта</t>
         </is>
@@ -514,24 +520,29 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>VK-C2022 (2) Набор кастрюль из стали,20x11.5 см, 22x12.5 см,24*13.5 см</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Набор кастрюль из стали,20x11.5 см, 22x12.5 см,24*13.5 см</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1659</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>1456</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>903.0769230769231</v>
       </c>
-      <c r="G2" s="4">
-        <f>F2*D2</f>
-        <v/>
-      </c>
       <c r="H2" s="4">
-        <f>F2*E2</f>
+        <f>G2*E2</f>
+        <v/>
+      </c>
+      <c r="I2" s="4">
+        <f>G2*F2</f>
         <v/>
       </c>
     </row>
@@ -546,24 +557,29 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>SP-20252 (6) Ковш аллюминевый с крышкой, 1,5л</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>Ковш аллюминевый с крышкой, 1,5л</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>294.6153846153846</v>
       </c>
-      <c r="G3" s="4">
-        <f>F3*D3</f>
-        <v/>
-      </c>
       <c r="H3" s="4">
-        <f>F3*E3</f>
+        <f>G3*E3</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>G3*F3</f>
         <v/>
       </c>
     </row>
@@ -578,24 +594,29 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>F2-20251 (6) Набор сковородок из аллюминия, размеры 24*5/28*5,5см</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>Набор сковородок из аллюминия, размеры 24*5/28*5,5см</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>453.8461538461538</v>
       </c>
-      <c r="G4" s="4">
-        <f>F4*D4</f>
-        <v/>
-      </c>
       <c r="H4" s="4">
-        <f>F4*E4</f>
+        <f>G4*E4</f>
+        <v/>
+      </c>
+      <c r="I4" s="4">
+        <f>G4*F4</f>
         <v/>
       </c>
     </row>
@@ -610,24 +631,29 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>F1-20253 (6) Сотейник из аллюминия,28*5,5см</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>Сотейник из аллюминия,28*5,5см</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>349.2307692307692</v>
       </c>
-      <c r="G5" s="4">
-        <f>F5*D5</f>
-        <v/>
-      </c>
       <c r="H5" s="4">
-        <f>F5*E5</f>
+        <f>G5*E5</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>G5*F5</f>
         <v/>
       </c>
     </row>
@@ -642,24 +668,29 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250101 (6) Френч-пресс, 600мл,стекло/сталь</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>Френч-пресс, 600мл,стекло/сталь</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>1652</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>1449</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>203.8461538461538</v>
       </c>
-      <c r="G6" s="4">
-        <f>F6*D6</f>
-        <v/>
-      </c>
       <c r="H6" s="4">
-        <f>F6*E6</f>
+        <f>G6*E6</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>G6*F6</f>
         <v/>
       </c>
     </row>
@@ -674,24 +705,29 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250102 (20) Набор кухонных принадлежностей(половник,ложка, толкушка,лопатка),нейлон</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Набор кухонных принадлежностей(половник,ложка, толкушка,лопатка),нейлон  KBF25-250102-20               </t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>128.4615384615385</v>
       </c>
-      <c r="G7" s="4">
-        <f>F7*D7</f>
-        <v/>
-      </c>
       <c r="H7" s="4">
-        <f>F7*E7</f>
+        <f>G7*E7</f>
+        <v/>
+      </c>
+      <c r="I7" s="4">
+        <f>G7*F7</f>
         <v/>
       </c>
     </row>
@@ -706,24 +742,29 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250110 (500) Овощечистка, размер 18,5*2,6см, нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>Овощечистка, размер 18,5*2,6см, нержавеющая сталь</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>14.65384615384615</v>
       </c>
-      <c r="G8" s="4">
-        <f>F8*D8</f>
-        <v/>
-      </c>
       <c r="H8" s="4">
-        <f>F8*E8</f>
+        <f>G8*E8</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>G8*F8</f>
         <v/>
       </c>
     </row>
@@ -738,24 +779,29 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250103 (64) Штопор, размер 17*5,2 см, пластик/сталь</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>Штопор, размер 17*5,2 см, пластик/сталь</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>52.48461538461539</v>
       </c>
-      <c r="G9" s="4">
-        <f>F9*D9</f>
-        <v/>
-      </c>
       <c r="H9" s="4">
-        <f>F9*E9</f>
+        <f>G9*E9</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>G9*F9</f>
         <v/>
       </c>
     </row>
@@ -770,24 +816,29 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250104 (50) Точилка для ножей, размер 29*7,6см</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>Точилка для ножей, размер 29*7,6см</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>144.1076923076923</v>
       </c>
-      <c r="G10" s="4">
-        <f>F10*D10</f>
-        <v/>
-      </c>
       <c r="H10" s="4">
-        <f>F10*E10</f>
+        <f>G10*E10</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>G10*F10</f>
         <v/>
       </c>
     </row>
@@ -801,6 +852,11 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>J1702 (20) Набор столовых приборов(ножи, вилки, ложки чайные, ложки столовые), сталь</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Набор столовых приборов(ножи, вилки, ложки чайные, ложки столовые), сталь:Ложка столовая 6 шт
  Вилка столовая  6 шт
@@ -809,21 +865,21 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>1457</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>301.5384615384615</v>
       </c>
-      <c r="G11" s="4">
-        <f>F11*D11</f>
-        <v/>
-      </c>
       <c r="H11" s="4">
-        <f>F11*E11</f>
+        <f>G11*E11</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>G11*F11</f>
         <v/>
       </c>
     </row>
@@ -838,24 +894,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250105 (44) Набор ножей,сталь</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Набор ножей,сталь</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>1462</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>376.9230769230769</v>
       </c>
-      <c r="G12" s="4">
-        <f>F12*D12</f>
-        <v/>
-      </c>
       <c r="H12" s="4">
-        <f>F12*E12</f>
+        <f>G12*E12</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>G12*F12</f>
         <v/>
       </c>
     </row>
@@ -870,24 +931,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>ZY-303S (12) Стеклянный электрический чайник,2 литра</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Стеклянный электрический чайник,2 литра</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>1656</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>1453</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>186.1538461538462</v>
       </c>
-      <c r="G13" s="4">
-        <f>F13*D13</f>
-        <v/>
-      </c>
       <c r="H13" s="4">
-        <f>F13*E13</f>
+        <f>G13*E13</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>G13*F13</f>
         <v/>
       </c>
     </row>
@@ -902,24 +968,29 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>KJ-229 (3) Электрический гриль,220-240 В, 50/60 Гц, 2000 Вт</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Электрический гриль,220-240 В, 50/60 Гц, 2000 Вт</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>1659</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>1456</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1023.846153846154</v>
       </c>
-      <c r="G14" s="4">
-        <f>F14*D14</f>
-        <v/>
-      </c>
       <c r="H14" s="4">
-        <f>F14*E14</f>
+        <f>G14*E14</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>G14*F14</f>
         <v/>
       </c>
     </row>
@@ -934,24 +1005,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>MK-666 (4) Кофеварка,  пластик/алюминий ,220-240 В,50/60 Гц,850 Вт</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Кофеварка,  пластик/алюминий ,220-240 В,50/60 Гц,850 Вт</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>1658</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1384.946153846154</v>
       </c>
-      <c r="G15" s="4">
-        <f>F15*D15</f>
-        <v/>
-      </c>
       <c r="H15" s="4">
-        <f>F15*E15</f>
+        <f>G15*E15</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>G15*F15</f>
         <v/>
       </c>
     </row>
@@ -966,24 +1042,29 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1337 (50) Держатель для полотенца, 48*7,8*10,5см</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Держатель для полотенца, 48*7,8*10,5см</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>3320</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>2925</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>51.79230769230769</v>
       </c>
-      <c r="G16" s="4">
-        <f>F16*D16</f>
-        <v/>
-      </c>
       <c r="H16" s="4">
-        <f>F16*E16</f>
+        <f>G16*E16</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>G16*F16</f>
         <v/>
       </c>
     </row>
@@ -998,24 +1079,29 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>311G-001-TR (6) Блюдо прямоугольное набор , размер 26,5 *17,5 см,2шт,фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>311G-001-TR</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1809</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="G17" s="4">
-        <f>F17*D17</f>
-        <v/>
-      </c>
       <c r="H17" s="4">
-        <f>F17*E17</f>
+        <f>G17*E17</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>G17*F17</f>
         <v/>
       </c>
     </row>
@@ -1030,24 +1116,29 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>96E-070-M1 (6) Набор кружек(6 шт), объем 340мл,белый, фарфор</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>96E-070-M1</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>1808</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>1602</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>174</v>
       </c>
-      <c r="G18" s="4">
-        <f>F18*D18</f>
-        <v/>
-      </c>
       <c r="H18" s="4">
-        <f>F18*E18</f>
+        <f>G18*E18</f>
+        <v/>
+      </c>
+      <c r="I18" s="4">
+        <f>G18*F18</f>
         <v/>
       </c>
     </row>
@@ -1062,24 +1153,29 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>311G-001-TSB (6) Набор чашка и блюдце ,объем 190мл,6шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>311G-001-TSB</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>1808</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>1602</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>394</v>
       </c>
-      <c r="G19" s="4">
-        <f>F19*D19</f>
-        <v/>
-      </c>
       <c r="H19" s="4">
-        <f>F19*E19</f>
+        <f>G19*E19</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>G19*F19</f>
         <v/>
       </c>
     </row>
@@ -1094,24 +1190,29 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>311G-001-SA (24) Набор розеток для соуса , диаметр 9,5см,6шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>311G-001-SA</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>1809</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="G20" s="4">
-        <f>F20*D20</f>
-        <v/>
-      </c>
       <c r="H20" s="4">
-        <f>F20*E20</f>
+        <f>G20*E20</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>G20*F20</f>
         <v/>
       </c>
     </row>
@@ -1126,24 +1227,29 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>96E-070-B1 (12) Набор салатников,диаметр 15,5см, 2шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>96E-070-B1</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>1809</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="G21" s="4">
-        <f>F21*D21</f>
-        <v/>
-      </c>
       <c r="H21" s="4">
-        <f>F21*E21</f>
+        <f>G21*E21</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>G21*F21</f>
         <v/>
       </c>
     </row>
@@ -1158,24 +1264,29 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>96E-070-SB1 (6) Набор салатников,диаметр 18см, 6шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>96E-070-SB1</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>1803</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>1597</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="G22" s="4">
-        <f>F22*D22</f>
-        <v/>
-      </c>
       <c r="H22" s="4">
-        <f>F22*E22</f>
+        <f>G22*E22</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>G22*F22</f>
         <v/>
       </c>
     </row>
@@ -1190,24 +1301,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>96E-070-SP1 (12) Набор салатников,диаметр 20,5см, 2шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>96E-070-SP1</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>1809</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="G23" s="4">
-        <f>F23*D23</f>
-        <v/>
-      </c>
       <c r="H23" s="4">
-        <f>F23*E23</f>
+        <f>G23*E23</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>G23*F23</f>
         <v/>
       </c>
     </row>
@@ -1222,24 +1338,29 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>96E-070-S1 (6) Набор тарелок десертных,диаметр 21,8см, 6шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>96E-070-S1</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>1803</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>1597</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>196</v>
       </c>
-      <c r="G24" s="4">
-        <f>F24*D24</f>
-        <v/>
-      </c>
       <c r="H24" s="4">
-        <f>F24*E24</f>
+        <f>G24*E24</f>
+        <v/>
+      </c>
+      <c r="I24" s="4">
+        <f>G24*F24</f>
         <v/>
       </c>
     </row>
@@ -1254,24 +1375,29 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>96E-070-D1 (3) Набор тарелок подстановочных,диаметр 27,4см, 6шт, фарфор, белый</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>96E-070-D1</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>1809</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>1603</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>286</v>
       </c>
-      <c r="G25" s="4">
-        <f>F25*D25</f>
-        <v/>
-      </c>
       <c r="H25" s="4">
-        <f>F25*E25</f>
+        <f>G25*E25</f>
+        <v/>
+      </c>
+      <c r="I25" s="4">
+        <f>G25*F25</f>
         <v/>
       </c>
     </row>
@@ -1286,24 +1412,29 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250106 (40) Фен для волос,1800 Вт</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>KBF25-250106-40</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>1698</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="G26" s="4">
-        <f>F26*D26</f>
-        <v/>
-      </c>
       <c r="H26" s="4">
-        <f>F26*E26</f>
+        <f>G26*E26</f>
+        <v/>
+      </c>
+      <c r="I26" s="4">
+        <f>G26*F26</f>
         <v/>
       </c>
     </row>
@@ -1318,24 +1449,29 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250107 (12) Ведро с педалью для ванной комнаты, 5 л, белое</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>KBF25-250107-12</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>1698</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="G27" s="4">
-        <f>F27*D27</f>
-        <v/>
-      </c>
       <c r="H27" s="4">
-        <f>F27*E27</f>
+        <f>G27*E27</f>
+        <v/>
+      </c>
+      <c r="I27" s="4">
+        <f>G27*F27</f>
         <v/>
       </c>
     </row>
@@ -1354,24 +1490,29 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250108 (6) Набор аксессуаров для ванной комнаты</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>KBF25-250108-6</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>1698</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>220</v>
       </c>
-      <c r="G28" s="4">
-        <f>F28*D28</f>
-        <v/>
-      </c>
       <c r="H28" s="4">
-        <f>F28*E28</f>
+        <f>G28*E28</f>
+        <v/>
+      </c>
+      <c r="I28" s="4">
+        <f>G28*F28</f>
         <v/>
       </c>
     </row>
@@ -1386,24 +1527,29 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>88292 (48) Держатель для туалетной бумаги, металл, хром+белый, вакуумное крепление</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>88292-48</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>1687</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>1495</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G29" s="4">
-        <f>F29*D29</f>
-        <v/>
-      </c>
       <c r="H29" s="4">
-        <f>F29*E29</f>
+        <f>G29*E29</f>
+        <v/>
+      </c>
+      <c r="I29" s="4">
+        <f>G29*F29</f>
         <v/>
       </c>
     </row>
@@ -1418,24 +1564,29 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>88301 (6) Полка для ванной комнаты угловая, 20*20*30см, железо</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>88301-6</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>1673</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>1481</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="G30" s="4">
-        <f>F30*D30</f>
-        <v/>
-      </c>
       <c r="H30" s="4">
-        <f>F30*E30</f>
+        <f>G30*E30</f>
+        <v/>
+      </c>
+      <c r="I30" s="4">
+        <f>G30*F30</f>
         <v/>
       </c>
     </row>
@@ -1450,24 +1601,29 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>KBF25-250109 (50) Коврик для ванной комнаты, 50*80см,бежевый</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>KBF25-250109-50</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>1698</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>1506</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="4">
-        <f>F31*D31</f>
-        <v/>
-      </c>
       <c r="H31" s="4">
-        <f>F31*E31</f>
+        <f>G31*E31</f>
+        <v/>
+      </c>
+      <c r="I31" s="4">
+        <f>G31*F31</f>
         <v/>
       </c>
     </row>
@@ -1482,24 +1638,29 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>BL005WT-50H (12) Корзина для белья, 48 литров</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>BL005WT-50H-12</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>1684</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1492</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>224</v>
       </c>
-      <c r="G32" s="4">
-        <f>F32*D32</f>
-        <v/>
-      </c>
       <c r="H32" s="4">
-        <f>F32*E32</f>
+        <f>G32*E32</f>
+        <v/>
+      </c>
+      <c r="I32" s="4">
+        <f>G32*F32</f>
         <v/>
       </c>
     </row>
@@ -1510,24 +1671,29 @@
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>MZ2501 (24) Искусственное растение ,высота 15см</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>MZ2501</t>
         </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>359</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>359</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="G33" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="G33" s="4">
-        <f>F33*D33</f>
-        <v/>
-      </c>
       <c r="H33" s="4">
-        <f>F33*E33</f>
+        <f>G33*E33</f>
+        <v/>
+      </c>
+      <c r="I33" s="4">
+        <f>G33*F33</f>
         <v/>
       </c>
     </row>
@@ -1538,24 +1704,29 @@
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>KA2-2309306 (12) Декоративное настольное зеркало, высота 20,5см,пластик</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>KA2-2309306</t>
         </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>371</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>371</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="3" t="n">
+        <v>371</v>
+      </c>
+      <c r="G34" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="G34" s="4">
-        <f>F34*D34</f>
-        <v/>
-      </c>
       <c r="H34" s="4">
-        <f>F34*E34</f>
+        <f>G34*E34</f>
+        <v/>
+      </c>
+      <c r="I34" s="4">
+        <f>G34*F34</f>
         <v/>
       </c>
     </row>
@@ -1566,24 +1737,29 @@
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>KB08-25022108 (4) Декоративное настольное зеркало, высота 35см,железо</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>KB08-25022108</t>
         </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>803</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>803</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="3" t="n">
+        <v>803</v>
+      </c>
+      <c r="G35" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="G35" s="4">
-        <f>F35*D35</f>
-        <v/>
-      </c>
       <c r="H35" s="4">
-        <f>F35*E35</f>
+        <f>G35*E35</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>G35*F35</f>
         <v/>
       </c>
     </row>
@@ -1594,24 +1770,29 @@
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>KB405-H1962 (12) Декоративная ваза, высота 20см, ассорти</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>KB405-H1962</t>
         </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>239</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="G36" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="G36" s="4">
-        <f>F36*D36</f>
-        <v/>
-      </c>
       <c r="H36" s="4">
-        <f>F36*E36</f>
+        <f>G36*E36</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>G36*F36</f>
         <v/>
       </c>
     </row>
@@ -1622,24 +1803,29 @@
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>KB45-6898-1 (8) Стол журнальный, высота 35.5см, ассорти</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>KB45-6898-1</t>
         </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>519</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>519</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="3" t="n">
+        <v>519</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="G37" s="4">
-        <f>F37*D37</f>
-        <v/>
-      </c>
       <c r="H37" s="4">
-        <f>F37*E37</f>
+        <f>G37*E37</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>G37*F37</f>
         <v/>
       </c>
     </row>
@@ -1650,24 +1836,29 @@
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>MC9379 (10) Часы настенные,цвет розовый,диаметр 30,5см</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>МС9379</t>
         </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>649</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>649</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="G38" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="G38" s="4">
-        <f>F38*D38</f>
-        <v/>
-      </c>
       <c r="H38" s="4">
-        <f>F38*E38</f>
+        <f>G38*E38</f>
+        <v/>
+      </c>
+      <c r="I38" s="4">
+        <f>G38*F38</f>
         <v/>
       </c>
     </row>
@@ -1678,24 +1869,29 @@
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>KB85-25022111 (24) Декоративная фоторамка,длина 20см,мдф, фиолетовый</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>KB85-25022111</t>
         </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>143</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="G39" s="4">
-        <f>F39*D39</f>
-        <v/>
-      </c>
       <c r="H39" s="4">
-        <f>F39*E39</f>
+        <f>G39*E39</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>G39*F39</f>
         <v/>
       </c>
     </row>
@@ -1706,24 +1902,29 @@
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>KA2-2309094 (12) Декоративное настольное зеркало, высота 17,7см,пластик</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>KA2-2309094</t>
         </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>911</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>911</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="3" t="n">
+        <v>911</v>
+      </c>
+      <c r="G40" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="G40" s="4">
-        <f>F40*D40</f>
-        <v/>
-      </c>
       <c r="H40" s="4">
-        <f>F40*E40</f>
+        <f>G40*E40</f>
+        <v/>
+      </c>
+      <c r="I40" s="4">
+        <f>G40*F40</f>
         <v/>
       </c>
     </row>
@@ -1734,24 +1935,29 @@
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>KB85-25022112 (24) Декоративная фоторамка,длина 20см,мдф, голубой</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>KB85-25022112</t>
         </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>47</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G41" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="G41" s="4">
-        <f>F41*D41</f>
-        <v/>
-      </c>
       <c r="H41" s="4">
-        <f>F41*E41</f>
+        <f>G41*E41</f>
+        <v/>
+      </c>
+      <c r="I41" s="4">
+        <f>G41*F41</f>
         <v/>
       </c>
     </row>
@@ -1762,24 +1968,29 @@
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>KB85-25022113 (24) Декоративная фоторамка,длина 20см,мдф, оранжевый</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>KB85-25022113</t>
         </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>47</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G42" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="G42" s="4">
-        <f>F42*D42</f>
-        <v/>
-      </c>
       <c r="H42" s="4">
-        <f>F42*E42</f>
+        <f>G42*E42</f>
+        <v/>
+      </c>
+      <c r="I42" s="4">
+        <f>G42*F42</f>
         <v/>
       </c>
     </row>
@@ -1790,24 +2001,29 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>KB142-052901 (4) Стол журнальный, высота 45.2см, белый</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>KB142-052901</t>
         </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>503</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="G43" s="4" t="n">
         <v>274</v>
       </c>
-      <c r="G43" s="4">
-        <f>F43*D43</f>
-        <v/>
-      </c>
       <c r="H43" s="4">
-        <f>F43*E43</f>
+        <f>G43*E43</f>
+        <v/>
+      </c>
+      <c r="I43" s="4">
+        <f>G43*F43</f>
         <v/>
       </c>
     </row>
@@ -1818,24 +2034,29 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>KB405-0827 (36) Статуэтка "Олень",керамика, высота 25см</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>KB405-0827</t>
         </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>323</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>323</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="3" t="n">
+        <v>323</v>
+      </c>
+      <c r="G44" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="G44" s="4">
-        <f>F44*D44</f>
-        <v/>
-      </c>
       <c r="H44" s="4">
-        <f>F44*E44</f>
+        <f>G44*E44</f>
+        <v/>
+      </c>
+      <c r="I44" s="4">
+        <f>G44*F44</f>
         <v/>
       </c>
     </row>
@@ -1846,24 +2067,29 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>DCA001 (36) Статуэтка "Медведь",керамика, высота 10см</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>DCA001</t>
         </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>503</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="G45" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="G45" s="4">
-        <f>F45*D45</f>
-        <v/>
-      </c>
       <c r="H45" s="4">
-        <f>F45*E45</f>
+        <f>G45*E45</f>
+        <v/>
+      </c>
+      <c r="I45" s="4">
+        <f>G45*F45</f>
         <v/>
       </c>
     </row>
@@ -1874,24 +2100,29 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>DCA002 (36) Статуэтка "Бегемот",керамика,высота 14см</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>DCA002</t>
         </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>359</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>359</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="G46" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="G46" s="4">
-        <f>F46*D46</f>
-        <v/>
-      </c>
       <c r="H46" s="4">
-        <f>F46*E46</f>
+        <f>G46*E46</f>
+        <v/>
+      </c>
+      <c r="I46" s="4">
+        <f>G46*F46</f>
         <v/>
       </c>
     </row>
@@ -1902,50 +2133,56 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>KB405-25022110 (20) Статуэтка "Мишка",высота 19см,зеленый</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
           <t>KB405-25022110</t>
         </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>679</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>679</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="3" t="n">
+        <v>679</v>
+      </c>
+      <c r="G47" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="G47" s="4">
-        <f>F47*D47</f>
-        <v/>
-      </c>
       <c r="H47" s="4">
-        <f>F47*E47</f>
+        <f>G47*E47</f>
+        <v/>
+      </c>
+      <c r="I47" s="4">
+        <f>G47*F47</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="n"/>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C48" s="1" t="n"/>
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>ИТОГО:</t>
         </is>
-      </c>
-      <c r="D48" s="5">
-        <f>SUM(D2:D47)</f>
-        <v/>
       </c>
       <c r="E48" s="5">
         <f>SUM(E2:E47)</f>
         <v/>
       </c>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6">
-        <f>SUM(G2:G47)</f>
-        <v/>
-      </c>
+      <c r="F48" s="5">
+        <f>SUM(F2:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="6" t="n"/>
       <c r="H48" s="6">
         <f>SUM(H2:H47)</f>
+        <v/>
+      </c>
+      <c r="I48" s="6">
+        <f>SUM(I2:I47)</f>
         <v/>
       </c>
     </row>
